--- a/artfynd/A 24531-2024 artfynd.xlsx
+++ b/artfynd/A 24531-2024 artfynd.xlsx
@@ -1025,7 +1025,7 @@
         <v>111668242</v>
       </c>
       <c r="B5" t="n">
-        <v>89235</v>
+        <v>89237</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 24531-2024 artfynd.xlsx
+++ b/artfynd/A 24531-2024 artfynd.xlsx
@@ -1025,7 +1025,7 @@
         <v>111668242</v>
       </c>
       <c r="B5" t="n">
-        <v>89237</v>
+        <v>89239</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 24531-2024 artfynd.xlsx
+++ b/artfynd/A 24531-2024 artfynd.xlsx
@@ -1025,7 +1025,7 @@
         <v>111668242</v>
       </c>
       <c r="B5" t="n">
-        <v>89239</v>
+        <v>89241</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
